--- a/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1002案.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1002案.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>受付の QR・名札差替え・急ぎの印刷</t>
+          <t>Sentio QR の案内カード（当日）、名札差替え、急ぎの印刷</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>QR コードと評価フォームの掲示は神戸で印刷して持参し、現地印刷は差替え分だけにする。Dorsett・EXPO のビジネスセンター有無は Sylvia に確認（Hotel Mi はなし）</t>
+          <t>Sentio の QR/URL は共有開始の操作をした時点で発行され、6 時間で失効するため事前印刷はできない。28 日 12:40・29 日 08:55 の共有開始直後に、このプリンターでテーブル用案内カードを印刷する（Sentio のためにプリンターは必須）。評価フォームの QR など日時に依らないものは神戸で印刷して持参。Dorsett・EXPO のビジネスセンター有無は Sylvia に確認（Hotel Mi はなし）</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>有線 LAN は AV 卓。会場ミキサーからの音声入力は業者と要調整</t>
+          <t>共有 URL は共有開始で発行され 6 時間で失効。QR の掲示・印刷は共有開始直後に行う。有線 LAN は AV 卓。会場ミキサーからの音声入力は業者と要調整</t>
         </is>
       </c>
     </row>

--- a/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1002案.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1002案.xlsx
@@ -569,17 +569,17 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>荒木田・児玉・藤中（各 1〜2 本）</t>
+          <t>荒木田（日本酒3本）、児玉さん・藤中さん（ウイスキー各1本）</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>荒木田 NH843／児玉 NH803／藤中 TR819（25 日）</t>
+          <t>荒木田 NH843（羽田）／児玉さん NH803／藤中さん TR819（25日）</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>児玉 9/24 案。免税店購入なら空港で各自購入。預け入れ不可の液体は手荷物に注意（免税袋）</t>
+          <t>荒木田は羽田発で神戸の荷物を持てないため、羽田の免税店で日本酒3本を購入して持参。ウイスキー2本は児玉さん・藤中さんが各1本。液体は免税袋のまま手荷物</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>荒木田（カメラ本体）＋池田（三脚）</t>
+          <t>塩見さん（カメラ本体・バッテリー・SD）、森川部長（三脚）。操作は荒木田</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>荒木田 NH843／池田 SQ619</t>
+          <t>10/26 TG623（関空→バンコク→SIN）</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>操作は ADRC 職員。業者とのオンライン会議で接続を確認してから持込内容を確定</t>
+          <t>神戸の機材は神戸発の職員が運ぶ（荒木田は羽田発）。カメラ本体は手荷物、三脚は預け入れ。乗継ぎがあるので三脚はケースに入れて名札を付ける。業者とのオンライン会議で接続を確認してから持込内容を確定</t>
         </is>
       </c>
     </row>
@@ -729,17 +729,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>荒木田・池田</t>
+          <t>藤本さん（Zoomホスト用PC・HDMIキャプチャ）、池田さん（演台用PC・変換アダプタ）</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>藤本さん TR819（26日）／池田さん SQ619</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Webinar ホストは神戸（中村）、現地は共同ホスト。演台 PC は TS 発表スライド集約用</t>
+          <t>いずれも手荷物。Webinarホストは神戸（中村さん）、現地は共同ホスト。演台PCはTS発表スライド集約用</t>
         </is>
       </c>
     </row>
@@ -769,17 +769,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>荒木田（設定）・中村（神戸で事前設定）</t>
+          <t>藤本さん（Sentio用PCまたはタブレット・外部マイク）。設定は荒木田と中村さん</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>藤本さん TR819（26日）</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>共有 URL は共有開始で発行され 6 時間で失効。QR の掲示・印刷は共有開始直後に行う。有線 LAN は AV 卓。会場ミキサーからの音声入力は業者と要調整</t>
+          <t>共有URLは共有開始で発行され6時間で失効。QRの掲示・印刷は共有開始直後に行う。有線LANはAV卓。会場ミキサーからの音声入力は業者と要調整</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Gerry（吉田はジュネーブ発のため神戸から持ち出せない）</t>
+          <t>Gerryさん（吉田さんはジュネーブ発、荒木田は羽田発のため神戸の物を持てない）</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>カメラ・PC は手荷物</t>
+          <t>羽田発のため神戸の機材は持てない。羽田の免税店で日本酒3本を購入</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Annual Report</t>
+          <t>Annual Report、Zoomホスト用PC、Sentio用機器</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>バナーフレームの代替候補。乗継ぎありで預け入れは要注意</t>
+          <t>カメラ本体・三脚。バナーフレームの代替候補。乗継ぎありで預け入れは要注意</t>
         </is>
       </c>
     </row>
